--- a/ig/DM-MAI-2026/CodeSystem-concept-properties.xlsx
+++ b/ig/DM-MAI-2026/CodeSystem-concept-properties.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="156">
   <si>
     <t>Property</t>
   </si>
@@ -115,7 +115,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>Code</t>
@@ -212,6 +212,15 @@
   </si>
   <si>
     <t>Propriété permettant de spécifier les codes exclusifs appartenant au RPPS</t>
+  </si>
+  <si>
+    <t>specialisationFiness</t>
+  </si>
+  <si>
+    <t>Specialisation FINESS</t>
+  </si>
+  <si>
+    <t>Propriété permettant de spécifier les codes exclusifs appartenant à FINESS</t>
   </si>
   <si>
     <t>ror</t>
@@ -812,7 +821,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1333,6 +1342,20 @@
         <v>152</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="D38" t="s" s="2">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
